--- a/data/trans_dic/P12_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,57</t>
+          <t>2,82; 5,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,49</t>
+          <t>6,33; 10,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,08</t>
+          <t>7,48; 11,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,09</t>
+          <t>7,52; 12,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,68</t>
+          <t>4,11; 7,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 16,64</t>
+          <t>11,47; 16,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,51</t>
+          <t>11,33; 16,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,23</t>
+          <t>10,55; 14,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,06</t>
+          <t>3,78; 6,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,91</t>
+          <t>9,48; 12,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,61</t>
+          <t>9,96; 13,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,53</t>
+          <t>9,67; 12,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,63</t>
+          <t>4,55; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,11</t>
+          <t>6,33; 10,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,15</t>
+          <t>4,29; 7,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,9</t>
+          <t>4,04; 11,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,0</t>
+          <t>7,1; 10,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 15,96</t>
+          <t>11,53; 16,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,21</t>
+          <t>7,46; 11,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,01</t>
+          <t>13,22; 17,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,67</t>
+          <t>6,32; 8,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,46</t>
+          <t>9,43; 12,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,76</t>
+          <t>6,35; 8,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,22</t>
+          <t>7,24; 13,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,13</t>
+          <t>3,4; 7,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,23</t>
+          <t>4,98; 9,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,99</t>
+          <t>5,17; 9,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,03</t>
+          <t>8,43; 14,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,68</t>
+          <t>5,9; 9,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 14,16</t>
+          <t>9,11; 14,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,15</t>
+          <t>8,77; 13,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,57</t>
+          <t>4,47; 12,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,71</t>
+          <t>5,08; 7,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 10,89</t>
+          <t>7,7; 10,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,45</t>
+          <t>7,47; 10,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,23</t>
+          <t>6,51; 12,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,42</t>
+          <t>3,79; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 10,78</t>
+          <t>7,06; 10,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,27</t>
+          <t>6,55; 9,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,65</t>
+          <t>9,48; 13,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,57</t>
+          <t>8,82; 12,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,02</t>
+          <t>11,68; 16,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 15,74</t>
+          <t>11,37; 15,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,27</t>
+          <t>12,18; 17,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,13</t>
+          <t>6,79; 9,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,02</t>
+          <t>10,01; 13,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,61</t>
+          <t>9,62; 12,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 14,97</t>
+          <t>11,86; 15,0</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,86</t>
+          <t>4,34; 5,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,11</t>
+          <t>7,12; 9,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,35</t>
+          <t>6,58; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,34</t>
+          <t>7,69; 11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,46</t>
+          <t>7,61; 9,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,52</t>
+          <t>12,05; 14,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,87</t>
+          <t>10,63; 12,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,39</t>
+          <t>10,52; 14,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,46</t>
+          <t>6,19; 7,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,34</t>
+          <t>8,91; 10,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 12,51</t>
+          <t>9,89; 12,49</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18609; 38680</t>
+          <t>19583; 39112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44050; 73666</t>
+          <t>44434; 74815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50417; 81262</t>
+          <t>50305; 79396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47362; 76665</t>
+          <t>47700; 77171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27865; 52855</t>
+          <t>28309; 54128</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79503; 115659</t>
+          <t>79741; 116390</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76363; 110821</t>
+          <t>76050; 112599</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70285; 95898</t>
+          <t>71093; 95899</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51848; 83821</t>
+          <t>52220; 83478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131439; 180428</t>
+          <t>132506; 180534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136174; 182882</t>
+          <t>133827; 183075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>125967; 163891</t>
+          <t>126522; 165353</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43331; 73379</t>
+          <t>43792; 74545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65842; 102645</t>
+          <t>64299; 102373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43820; 72991</t>
+          <t>43863; 74851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49861; 129964</t>
+          <t>48196; 131904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68935; 106551</t>
+          <t>68721; 104112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119082; 164368</t>
+          <t>118801; 169095</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78875; 116918</t>
+          <t>77814; 118302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>125935; 162846</t>
+          <t>126577; 164456</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120952; 167377</t>
+          <t>122004; 168748</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193510; 254884</t>
+          <t>192968; 253472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129464; 180771</t>
+          <t>131169; 178765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>167021; 284201</t>
+          <t>155587; 282532</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24621; 48374</t>
+          <t>23047; 48318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39940; 69827</t>
+          <t>37646; 68398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39608; 68251</t>
+          <t>39299; 68678</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60195; 98672</t>
+          <t>59294; 100450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39065; 66166</t>
+          <t>40330; 67295</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70523; 109761</t>
+          <t>70631; 108981</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69119; 102940</t>
+          <t>68641; 104766</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45887; 117265</t>
+          <t>41734; 115971</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69935; 105054</t>
+          <t>69163; 105485</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119345; 166795</t>
+          <t>117967; 163497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115662; 161105</t>
+          <t>115208; 161875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>106312; 199988</t>
+          <t>106526; 198361</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34888; 60496</t>
+          <t>35742; 61259</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67310; 102079</t>
+          <t>66811; 102796</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60129; 96094</t>
+          <t>61300; 93256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88162; 126515</t>
+          <t>87839; 125180</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91818; 130596</t>
+          <t>91618; 132378</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123158; 168481</t>
+          <t>122902; 170518</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116106; 163789</t>
+          <t>118308; 164640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>131162; 189077</t>
+          <t>133327; 191857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>135040; 180888</t>
+          <t>134485; 182762</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>203306; 260287</t>
+          <t>200134; 261806</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192401; 249224</t>
+          <t>190053; 246188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>239688; 302681</t>
+          <t>239858; 303350</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>143463; 192159</t>
+          <t>142339; 191186</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>244051; 311769</t>
+          <t>243438; 310899</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>219954; 282827</t>
+          <t>222906; 283150</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261632; 391794</t>
+          <t>265822; 386179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>254823; 319623</t>
+          <t>257068; 322135</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>429410; 515675</t>
+          <t>428105; 514007</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>377743; 455323</t>
+          <t>376179; 454713</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>383620; 526372</t>
+          <t>384807; 527633</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>413707; 496793</t>
+          <t>411795; 487619</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>697227; 802929</t>
+          <t>697074; 802675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>617461; 715912</t>
+          <t>617307; 712009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>721084; 889857</t>
+          <t>704016; 888582</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,64</t>
+          <t>2,74; 5,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,65</t>
+          <t>6,59; 10,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,8</t>
+          <t>7,49; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,17</t>
+          <t>7,76; 12,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,86</t>
+          <t>4,11; 7,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 16,74</t>
+          <t>11,27; 16,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 16,78</t>
+          <t>11,46; 16,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,23</t>
+          <t>10,58; 14,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,04</t>
+          <t>3,83; 6,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,92</t>
+          <t>9,51; 12,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,62</t>
+          <t>10,08; 13,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 12,64</t>
+          <t>9,66; 12,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,75</t>
+          <t>4,5; 7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,08</t>
+          <t>6,57; 10,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,33</t>
+          <t>4,14; 7,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,06</t>
+          <t>7,48; 11,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,75</t>
+          <t>6,95; 10,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 16,42</t>
+          <t>11,58; 16,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,34</t>
+          <t>7,12; 11,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 17,18</t>
+          <t>13,51; 17,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,74</t>
+          <t>6,28; 8,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 12,39</t>
+          <t>9,47; 12,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,66</t>
+          <t>6,18; 8,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 13,14</t>
+          <t>11,12; 13,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,12</t>
+          <t>3,5; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,04</t>
+          <t>5,18; 8,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,04</t>
+          <t>5,09; 8,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 14,29</t>
+          <t>8,62; 13,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,84</t>
+          <t>5,71; 9,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 14,06</t>
+          <t>9,15; 14,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,39</t>
+          <t>8,75; 13,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 12,43</t>
+          <t>10,39; 14,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,74</t>
+          <t>5,03; 7,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,68</t>
+          <t>7,72; 10,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,5</t>
+          <t>7,34; 10,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 12,13</t>
+          <t>9,97; 13,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,5</t>
+          <t>3,7; 6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,86</t>
+          <t>7,09; 10,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,97</t>
+          <t>6,61; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,51</t>
+          <t>10,3; 14,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,75</t>
+          <t>8,73; 12,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 16,21</t>
+          <t>11,8; 16,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,82</t>
+          <t>11,44; 16,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,52</t>
+          <t>15,14; 19,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,23</t>
+          <t>6,72; 9,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 13,1</t>
+          <t>10,1; 13,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 12,46</t>
+          <t>9,68; 12,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,0</t>
+          <t>13,42; 16,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,83</t>
+          <t>4,37; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,09</t>
+          <t>7,17; 9,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,35</t>
+          <t>6,47; 8,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,17</t>
+          <t>9,49; 11,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,53</t>
+          <t>7,6; 9,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 14,47</t>
+          <t>12,15; 14,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 12,85</t>
+          <t>10,65; 12,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,42</t>
+          <t>13,59; 15,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,33</t>
+          <t>6,24; 7,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 11,51</t>
+          <t>9,97; 11,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,28</t>
+          <t>8,85; 10,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,49</t>
+          <t>11,9; 13,37</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82587</t>
+          <t>90810</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>143775</t>
+          <t>158900</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19583; 39112</t>
+          <t>19026; 38268</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44434; 74815</t>
+          <t>46262; 76500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50305; 79396</t>
+          <t>50376; 82564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47700; 77171</t>
+          <t>53473; 84071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28309; 54128</t>
+          <t>28285; 52049</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79741; 116390</t>
+          <t>78308; 115805</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76050; 112599</t>
+          <t>76882; 113248</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71093; 95899</t>
+          <t>77361; 105147</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52220; 83478</t>
+          <t>52999; 84094</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132506; 180534</t>
+          <t>132979; 179304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133827; 183075</t>
+          <t>135400; 181412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>126522; 165353</t>
+          <t>137273; 179481</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95407</t>
+          <t>96373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>143880</t>
+          <t>164056</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>239286</t>
+          <t>260429</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43792; 74545</t>
+          <t>43290; 75337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64299; 102373</t>
+          <t>66752; 103781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43863; 74851</t>
+          <t>42287; 73156</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48196; 131904</t>
+          <t>78391; 117376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68721; 104112</t>
+          <t>67288; 102182</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>118801; 169095</t>
+          <t>119292; 166261</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77814; 118302</t>
+          <t>74247; 115920</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>126577; 164456</t>
+          <t>144495; 188526</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122004; 168748</t>
+          <t>121264; 168576</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>192968; 253472</t>
+          <t>193775; 253647</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131169; 178765</t>
+          <t>127533; 177274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>155587; 282532</t>
+          <t>235508; 292498</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76633</t>
+          <t>86491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85229</t>
+          <t>100831</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>161862</t>
+          <t>187322</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23047; 48318</t>
+          <t>23766; 47141</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37646; 68398</t>
+          <t>39156; 67801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39299; 68678</t>
+          <t>38644; 67008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59294; 100450</t>
+          <t>69033; 109444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40330; 67295</t>
+          <t>39035; 65127</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70631; 108981</t>
+          <t>70937; 108624</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68641; 104766</t>
+          <t>68450; 105454</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41734; 115971</t>
+          <t>84334; 118467</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69163; 105485</t>
+          <t>68577; 105583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117967; 163497</t>
+          <t>118181; 165365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115208; 161875</t>
+          <t>113179; 161652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>106526; 198361</t>
+          <t>160809; 216403</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106168</t>
+          <t>121217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>166572</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>272740</t>
+          <t>311320</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35742; 61259</t>
+          <t>34834; 62052</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66811; 102796</t>
+          <t>67153; 101951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61300; 93256</t>
+          <t>61800; 94424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87839; 125180</t>
+          <t>101961; 145887</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91618; 132378</t>
+          <t>90708; 131423</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>122902; 170518</t>
+          <t>124168; 170696</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118308; 164640</t>
+          <t>119070; 166554</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>133327; 191857</t>
+          <t>169413; 213176</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>134485; 182762</t>
+          <t>133108; 181965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200134; 261806</t>
+          <t>201928; 262366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190053; 246188</t>
+          <t>191272; 249910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>239858; 303350</t>
+          <t>282938; 342099</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339395</t>
+          <t>372171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>478268</t>
+          <t>545799</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>817663</t>
+          <t>917970</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>142339; 191186</t>
+          <t>143211; 193234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>243438; 310899</t>
+          <t>245231; 309431</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222906; 283150</t>
+          <t>219243; 281575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>265822; 386179</t>
+          <t>334899; 414889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>257068; 322135</t>
+          <t>256718; 323281</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>428105; 514007</t>
+          <t>431634; 516370</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>376179; 454713</t>
+          <t>376754; 457968</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>384807; 527633</t>
+          <t>507321; 582410</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>411795; 487619</t>
+          <t>415159; 501040</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>697074; 802675</t>
+          <t>695485; 802469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>617307; 712009</t>
+          <t>613129; 715991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>704016; 888582</t>
+          <t>863725; 971068</t>
         </is>
       </c>
     </row>
